--- a/artfynd/A 16414-2023 artfynd.xlsx
+++ b/artfynd/A 16414-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16414-2023 artfynd.xlsx
+++ b/artfynd/A 16414-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>74739715</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387714.3109611872</v>
+        <v>387714</v>
       </c>
       <c r="R2" t="n">
-        <v>6670135.247123361</v>
+        <v>6670135</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -760,19 +755,9 @@
           <t>2018-11-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-11-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91511861</v>
+        <v>95985275</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -851,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387533.2362223705</v>
+        <v>387533</v>
       </c>
       <c r="R3" t="n">
-        <v>6670430.756170717</v>
+        <v>6670431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,22 +861,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>olika intensiva höstläten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,6 +905,125 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>91511861</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kärrmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>387533</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6670431</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fryksände</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-03-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-03-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jesper Berg Bylander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jesper Berg Bylander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16414-2023 artfynd.xlsx
+++ b/artfynd/A 16414-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74739715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95985275</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,8 +1039,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91511861</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>